--- a/data/trans_dic/P20D_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P20D_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo</t>
+          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,24; 73,95</t>
+          <t>32,13; 73,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,17; 77,44</t>
+          <t>38,69; 77,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,98; 70,29</t>
+          <t>40,86; 68,71</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>56,15; 87,11</t>
+          <t>56,78; 87,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,64; 57,73</t>
+          <t>21,1; 57,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,53; 68,92</t>
+          <t>44,32; 68,26</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58,93; 100,0</t>
+          <t>62,39; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 37,28</t>
+          <t>2,12; 35,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,15; 78,72</t>
+          <t>37,88; 82,59</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>58,54; 80,67</t>
+          <t>58,73; 80,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,7; 52,36</t>
+          <t>27,65; 53,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,5; 64,93</t>
+          <t>47,73; 65,21</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo</t>
+          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6230; 13861</t>
+          <t>6022; 13840</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5287; 10451</t>
+          <t>5222; 10417</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13213; 22662</t>
+          <t>13173; 22152</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18429; 28589</t>
+          <t>18634; 28798</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5597; 16448</t>
+          <t>6010; 16467</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27305; 42255</t>
+          <t>27172; 41853</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6312; 10712</t>
+          <t>6684; 10712</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>152; 2867</t>
+          <t>163; 2719</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6836; 14485</t>
+          <t>6971; 15197</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36456; 50242</t>
+          <t>36577; 50411</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13760; 26012</t>
+          <t>13734; 26597</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53182; 72689</t>
+          <t>53433; 73007</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P20D_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P20D_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,37%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,13; 73,83</t>
+          <t>30,79; 73,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38,69; 77,18</t>
+          <t>39,6; 75,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,86; 68,71</t>
+          <t>39,81; 68,19</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>58,6%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>56,78; 87,75</t>
+          <t>60,21; 89,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,1; 57,8</t>
+          <t>22,81; 59,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,32; 68,26</t>
+          <t>46,76; 69,11</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>56,91%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,39; 100,0</t>
+          <t>51,69; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 35,36</t>
+          <t>4,0; 43,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,88; 82,59</t>
+          <t>34,58; 76,75</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>58,73; 80,95</t>
+          <t>61,02; 82,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,65; 53,54</t>
+          <t>29,8; 54,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,73; 65,21</t>
+          <t>48,96; 65,03</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9913</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17779</t>
+          <t>19166</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6022; 13840</t>
+          <t>5992; 14364</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5222; 10417</t>
+          <t>6000; 11424</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13173; 22152</t>
+          <t>13780; 23601</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>24371</t>
+          <t>28550</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10114</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34486</t>
+          <t>40900</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18634; 28798</t>
+          <t>22609; 33477</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6010; 16467</t>
+          <t>7354; 19314</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27172; 41853</t>
+          <t>32634; 48235</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>11679</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6684; 10712</t>
+          <t>5784; 11188</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>163; 2719</t>
+          <t>373; 4089</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6971; 15197</t>
+          <t>7098; 15752</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>43963</t>
+          <t>48976</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>22770</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62928</t>
+          <t>71746</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36577; 50411</t>
+          <t>41618; 56405</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13734; 26597</t>
+          <t>16904; 30632</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53433; 73007</t>
+          <t>61161; 81240</t>
         </is>
       </c>
     </row>
